--- a/Content/Config/Data/DT_SkillConfig.xlsx
+++ b/Content/Config/Data/DT_SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\UnrealEngine\UEProject\FrontendUI\Content\Config\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{223FCAA3-D8DF-4231-94E6-512E117AF59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A62305-FB5D-4104-BB8D-83CB2CA9FDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{2C778187-25A6-4551-9EB6-C2C1EAC8F6EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -85,6 +85,14 @@
   </si>
   <si>
     <t>(Tags=Ability.Melee.Light)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AttackMontage</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Script/Engine.AnimMontage'/Game/Gameplay/Player/Montage/MA_Melee.MA_Melee'</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1057,7 +1065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A055F7F9-2A81-49D4-B1E3-5F3D418503E1}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -1066,11 +1074,12 @@
     <col min="4" max="4" width="24.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.9140625" customWidth="1"/>
     <col min="7" max="7" width="22.1640625" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
-    <col min="12" max="12" width="17.9140625" customWidth="1"/>
+    <col min="11" max="11" width="52.9140625" customWidth="1"/>
+    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="13" max="13" width="17.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1102,13 +1111,16 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1137,13 +1149,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="b">
+      <c r="M2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1171,10 +1186,10 @@
       <c r="J3">
         <v>0.5</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>18</v>
       </c>
-      <c r="L3" t="b">
+      <c r="M3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Content/Config/Data/DT_SkillConfig.xlsx
+++ b/Content/Config/Data/DT_SkillConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\UnrealEngine\UEProject\FrontendUI\Content\Config\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A62305-FB5D-4104-BB8D-83CB2CA9FDF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0E5A01-A49A-48EA-A6B5-1BD4D3025536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{2C778187-25A6-4551-9EB6-C2C1EAC8F6EE}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>Name</t>
   </si>
@@ -93,6 +93,34 @@
   </si>
   <si>
     <t>/Script/Engine.AnimMontage'/Game/Gameplay/Player/Montage/MA_Melee.MA_Melee'</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NSLOCTEXT(,,重攻击)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Healing</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Tag=Cost.MP)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Tag=Skill.Healing)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>(Tags=Skill.Healing)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>NSLOCTEXT(,,Heal)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>/Script/Engine.Texture2D'/Game/Assets/UI/Icons/HealthRegen.HealthRegen'</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1065,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A055F7F9-2A81-49D4-B1E3-5F3D418503E1}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.5" customWidth="1"/>
@@ -1074,7 +1102,8 @@
     <col min="4" max="4" width="24.33203125" customWidth="1"/>
     <col min="6" max="6" width="17.9140625" customWidth="1"/>
     <col min="7" max="7" width="22.1640625" customWidth="1"/>
-    <col min="11" max="11" width="52.9140625" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="27.83203125" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="17.9140625" customWidth="1"/>
   </cols>
@@ -1166,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -1190,11 +1219,50 @@
         <v>18</v>
       </c>
       <c r="M3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4">
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>15</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>26</v>
+      </c>
+      <c r="M4" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>